--- a/rules_data/Fiche_BAR.xlsx
+++ b/rules_data/Fiche_BAR.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LoïcGORMAND\Documents\Archives\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BD6C4C9-0602-4346-8433-D571302DCE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="569">
   <si>
     <t>FICHE</t>
   </si>
@@ -1001,28 +1007,6 @@
 ▪ si cas installatation individuelle :
 ▪ la classe énergétique
 ▪ la puissance pondérée en WThC pour un T4 avec sdb et WC</t>
-  </si>
-  <si>
-    <t>▪ Nombre de caissons
-▪ Nombre de bouche d'exctraction
-▪ Nombre d'entrée d'air
-▪ Marque et références de ces éléments OU le type (hygroréglable ou autoréglable)
-▪ Puissance électrique pondérée absorbée</t>
-  </si>
-  <si>
-    <t>▪ Nombre de caissons
-▪ Nombre de bouche d'extraction
-▪ Nombre d'entrée d'air
-▪ Marque et références de ces éléments OU le type (hygroréglable ou autoréglable)
-▪ Puissance électrique pondérée absorbée</t>
-  </si>
-  <si>
-    <t>▪ Nombre de caissons
-▪ Nombre de bouche d'extraction
-▪ Nombre d'entrée d'air
-▪ Marque et références de ces éléments OU le type (hygroréglable A ou B, ou basse pression)
-▪ Puissance électrique pondérée absorbée
-▪ si nécessaire, remplacement ou mise en place des gaines de ventilation</t>
   </si>
   <si>
     <t>▪ Nombre de PAC air/air installées
@@ -1486,10 +1470,15 @@
 ▪ nombre de logements en installation collective</t>
   </si>
   <si>
-    <t>▪ Marques et références du caisson, des bouches d'extractions et des entrée d'air, type d'énergie de chauffage,  puissance électrique absorbée pondérée, surface habitable en maison ou nombre de logement en collectif</t>
-  </si>
-  <si>
-    <t>▪ Marques et références du caisson, des bouches d'extractions et des entrée d'air, type de ventilation, type d'énergie de chauffage,  numéro de l'avis technique, date de validité de l'avis technique, puissance électrique absorbée pondérée, surface habitable en installation individuelle ou nombre de logement en installation collective</t>
+    <t>▪ Type d'énergie de chauffage
+▪ Surface habitable (installation individuelle) ou nombre de logements (installation collective)</t>
+  </si>
+  <si>
+    <t>▪ Type de ventilation
+▪ Type d'énergie de chauffage
+▪ Numéro de l'avis technique
+▪ Date de validité de l'avis technique
+▪ Surface habitable (installation individuelle) ou nombre de logements (installation collective)</t>
   </si>
   <si>
     <t>▪ Surface des logements
@@ -2945,15 +2934,27 @@
     <t>BAR-TH-169
 BAR-TH-178</t>
   </si>
+  <si>
+    <t>▪ Nombre de caissons
+▪ Nombre de bouche d'exctraction
+▪ Nombre d'entrée d'air
+▪ Marque des entrées d'air
+▪ Référence des entrées d'air
+▪ Marque des bouches d'exctraction
+▪ Référence des bouches d'exctraction
+▪ Marque des caissons
+▪ Référence des caissons
+▪ Puissance électrique pondérée absorbée</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2982,22 +2983,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3035,7 +3047,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -3069,6 +3081,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3103,9 +3116,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3278,11 +3292,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K133"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="44.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" customWidth="1"/>
+    <col min="5" max="5" width="65.5546875" customWidth="1"/>
+    <col min="6" max="6" width="53.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3317,7 +3337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3334,19 +3354,19 @@
         <v>203</v>
       </c>
       <c r="F2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="I2" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -3363,22 +3383,22 @@
         <v>204</v>
       </c>
       <c r="F3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H3" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J3" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -3395,22 +3415,22 @@
         <v>205</v>
       </c>
       <c r="F4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H4" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I4" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J4" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -3427,22 +3447,22 @@
         <v>205</v>
       </c>
       <c r="F5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H5" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I5" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="J5" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -3459,19 +3479,19 @@
         <v>206</v>
       </c>
       <c r="G6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H6" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I6" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="J6" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3488,19 +3508,19 @@
         <v>206</v>
       </c>
       <c r="G7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H7" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I7" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="J7" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -3517,22 +3537,22 @@
         <v>207</v>
       </c>
       <c r="F8" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G8" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="I8" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J8" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -3548,14 +3568,20 @@
       <c r="E9" t="s">
         <v>208</v>
       </c>
+      <c r="F9" t="s">
+        <v>293</v>
+      </c>
+      <c r="G9" t="s">
+        <v>371</v>
+      </c>
       <c r="H9" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J9" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -3568,14 +3594,23 @@
       <c r="D10" s="1">
         <v>46508</v>
       </c>
+      <c r="E10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F10" t="s">
+        <v>293</v>
+      </c>
+      <c r="G10" t="s">
+        <v>371</v>
+      </c>
       <c r="H10" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J10" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3592,16 +3627,16 @@
         <v>207</v>
       </c>
       <c r="F11" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G11" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I11" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -3618,22 +3653,22 @@
         <v>209</v>
       </c>
       <c r="F12" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G12" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H12" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I12" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J12" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -3650,22 +3685,22 @@
         <v>210</v>
       </c>
       <c r="F13" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G13" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H13" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I13" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J13" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -3682,22 +3717,22 @@
         <v>210</v>
       </c>
       <c r="F14" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G14" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H14" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I14" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J14" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -3714,22 +3749,22 @@
         <v>210</v>
       </c>
       <c r="F15" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G15" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H15" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I15" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J15" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -3746,19 +3781,19 @@
         <v>211</v>
       </c>
       <c r="F16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G16" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I16" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J16" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3775,22 +3810,22 @@
         <v>212</v>
       </c>
       <c r="F17" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G17" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H17" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I17" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J17" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -3807,16 +3842,16 @@
         <v>207</v>
       </c>
       <c r="F18" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G18" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I18" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -3833,19 +3868,19 @@
         <v>207</v>
       </c>
       <c r="F19" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G19" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="H19" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I19" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -3862,22 +3897,22 @@
         <v>207</v>
       </c>
       <c r="F20" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G20" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="H20" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I20" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J20" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -3894,22 +3929,22 @@
         <v>207</v>
       </c>
       <c r="F21" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G21" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="H21" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I21" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J21" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -3926,19 +3961,19 @@
         <v>213</v>
       </c>
       <c r="F22" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G22" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I22" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K22" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -3955,22 +3990,22 @@
         <v>213</v>
       </c>
       <c r="F23" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G23" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="H23" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I23" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K23" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -3987,22 +4022,22 @@
         <v>214</v>
       </c>
       <c r="F24" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G24" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="H24" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I24" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K24" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -4019,16 +4054,16 @@
         <v>215</v>
       </c>
       <c r="F25" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G25" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="I25" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -4045,16 +4080,16 @@
         <v>216</v>
       </c>
       <c r="F26" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G26" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I26" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -4068,16 +4103,16 @@
         <v>217</v>
       </c>
       <c r="F27" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G27" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I27" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -4091,16 +4126,16 @@
         <v>218</v>
       </c>
       <c r="F28" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G28" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I28" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -4117,19 +4152,19 @@
         <v>219</v>
       </c>
       <c r="F29" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G29" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="H29" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="I29" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -4146,19 +4181,19 @@
         <v>219</v>
       </c>
       <c r="F30" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G30" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="H30" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="I30" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -4175,19 +4210,19 @@
         <v>220</v>
       </c>
       <c r="F31" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G31" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="H31" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="I31" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>41</v>
       </c>
@@ -4204,19 +4239,19 @@
         <v>221</v>
       </c>
       <c r="F32" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G32" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="H32" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I32" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -4233,19 +4268,19 @@
         <v>221</v>
       </c>
       <c r="F33" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G33" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="H33" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="I33" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>43</v>
       </c>
@@ -4262,19 +4297,19 @@
         <v>221</v>
       </c>
       <c r="F34" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G34" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="H34" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="I34" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -4291,19 +4326,19 @@
         <v>222</v>
       </c>
       <c r="F35" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G35" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="I35" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K35" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -4320,16 +4355,16 @@
         <v>223</v>
       </c>
       <c r="G36" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H36" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="I36" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -4346,19 +4381,19 @@
         <v>223</v>
       </c>
       <c r="G37" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H37" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="I37" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K37" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>47</v>
       </c>
@@ -4372,19 +4407,19 @@
         <v>224</v>
       </c>
       <c r="F38" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G38" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I38" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K38" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -4401,16 +4436,16 @@
         <v>225</v>
       </c>
       <c r="F39" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G39" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I39" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>49</v>
       </c>
@@ -4427,22 +4462,22 @@
         <v>226</v>
       </c>
       <c r="F40" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G40" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="H40" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="I40" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="J40" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -4459,19 +4494,19 @@
         <v>227</v>
       </c>
       <c r="F41" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G41" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I41" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="J41" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -4488,19 +4523,19 @@
         <v>228</v>
       </c>
       <c r="F42" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G42" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="I42" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J42" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>52</v>
       </c>
@@ -4517,19 +4552,19 @@
         <v>229</v>
       </c>
       <c r="F43" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G43" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="I43" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J43" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -4543,16 +4578,16 @@
         <v>230</v>
       </c>
       <c r="F44" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G44" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I44" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>54</v>
       </c>
@@ -4569,16 +4604,16 @@
         <v>231</v>
       </c>
       <c r="F45" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G45" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="I45" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -4595,19 +4630,19 @@
         <v>232</v>
       </c>
       <c r="F46" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G46" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H46" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I46" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>56</v>
       </c>
@@ -4624,22 +4659,22 @@
         <v>233</v>
       </c>
       <c r="F47" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G47" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H47" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="I47" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="J47" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -4656,13 +4691,13 @@
         <v>234</v>
       </c>
       <c r="G48" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="I48" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>58</v>
       </c>
@@ -4679,19 +4714,19 @@
         <v>235</v>
       </c>
       <c r="F49" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G49" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="H49" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="I49" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -4708,22 +4743,22 @@
         <v>236</v>
       </c>
       <c r="F50" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G50" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H50" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="I50" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J50" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -4740,25 +4775,25 @@
         <v>237</v>
       </c>
       <c r="F51" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G51" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="H51" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="I51" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="J51" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K51" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -4772,19 +4807,19 @@
         <v>238</v>
       </c>
       <c r="F52" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G52" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="I52" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K52" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>62</v>
       </c>
@@ -4801,19 +4836,19 @@
         <v>239</v>
       </c>
       <c r="F53" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G53" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I53" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K53" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>63</v>
       </c>
@@ -4830,16 +4865,16 @@
         <v>240</v>
       </c>
       <c r="F54" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G54" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I54" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>64</v>
       </c>
@@ -4856,19 +4891,19 @@
         <v>241</v>
       </c>
       <c r="F55" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G55" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="I55" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K55" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>65</v>
       </c>
@@ -4885,19 +4920,19 @@
         <v>242</v>
       </c>
       <c r="F56" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G56" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="I56" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K56" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -4914,16 +4949,16 @@
         <v>243</v>
       </c>
       <c r="F57" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G57" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="I57" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>67</v>
       </c>
@@ -4940,22 +4975,22 @@
         <v>244</v>
       </c>
       <c r="F58" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G58" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="H58" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I58" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J58" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>68</v>
       </c>
@@ -4972,22 +5007,22 @@
         <v>245</v>
       </c>
       <c r="F59" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G59" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H59" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I59" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J59" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="144" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -5000,20 +5035,20 @@
       <c r="D60" s="1">
         <v>43921</v>
       </c>
-      <c r="E60" t="s">
-        <v>246</v>
+      <c r="E60" s="2" t="s">
+        <v>568</v>
       </c>
       <c r="F60" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G60" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I60" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="144" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>70</v>
       </c>
@@ -5026,26 +5061,26 @@
       <c r="D61" s="1">
         <v>45291</v>
       </c>
-      <c r="E61" t="s">
-        <v>247</v>
+      <c r="E61" s="2" t="s">
+        <v>568</v>
       </c>
       <c r="F61" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G61" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="H61" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I61" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J61" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="144" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -5058,26 +5093,26 @@
       <c r="D62" s="1">
         <v>46934</v>
       </c>
-      <c r="E62" t="s">
-        <v>248</v>
+      <c r="E62" s="2" t="s">
+        <v>568</v>
       </c>
       <c r="F62" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G62" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="H62" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I62" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J62" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>72</v>
       </c>
@@ -5088,19 +5123,19 @@
         <v>43191</v>
       </c>
       <c r="E63" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F63" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G63" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="I63" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>73</v>
       </c>
@@ -5114,19 +5149,19 @@
         <v>45291</v>
       </c>
       <c r="E64" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F64" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="G64" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="I64" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -5140,19 +5175,19 @@
         <v>46753</v>
       </c>
       <c r="E65" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F65" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G65" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="I65" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>75</v>
       </c>
@@ -5166,19 +5201,19 @@
         <v>44104</v>
       </c>
       <c r="E66" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F66" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G66" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I66" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>76</v>
       </c>
@@ -5192,19 +5227,19 @@
         <v>44804</v>
       </c>
       <c r="E67" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F67" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G67" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I67" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -5218,19 +5253,19 @@
         <v>46022</v>
       </c>
       <c r="E68" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F68" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G68" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I68" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -5241,19 +5276,19 @@
         <v>46023</v>
       </c>
       <c r="E69" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F69" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G69" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I69" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -5264,19 +5299,19 @@
         <v>42767</v>
       </c>
       <c r="E70" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F70" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G70" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="I70" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -5290,22 +5325,22 @@
         <v>45992</v>
       </c>
       <c r="E71" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F71" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G71" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="I71" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="K71" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -5319,28 +5354,28 @@
         <v>47848</v>
       </c>
       <c r="E72" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F72" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G72" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="H72" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I72" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="J72" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="K72" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -5354,22 +5389,22 @@
         <v>43921</v>
       </c>
       <c r="E73" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F73" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G73" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="I73" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K73" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -5383,28 +5418,28 @@
         <v>45138</v>
       </c>
       <c r="E74" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F74" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G74" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H74" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="I74" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J74" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="K74" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -5418,28 +5453,28 @@
         <v>45596</v>
       </c>
       <c r="E75" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F75" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G75" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H75" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I75" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J75" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="K75" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -5453,19 +5488,19 @@
         <v>45960</v>
       </c>
       <c r="E76" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F76" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G76" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="I76" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -5479,22 +5514,22 @@
         <v>46022</v>
       </c>
       <c r="E77" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F77" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G77" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H77" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I77" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -5508,25 +5543,25 @@
         <v>47848</v>
       </c>
       <c r="E78" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F78" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G78" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H78" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I78" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K78" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -5540,19 +5575,19 @@
         <v>45901</v>
       </c>
       <c r="E79" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F79" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G79" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="I79" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -5566,19 +5601,19 @@
         <v>43921</v>
       </c>
       <c r="E80" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F80" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G80" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="I80" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>90</v>
       </c>
@@ -5589,22 +5624,22 @@
         <v>43922</v>
       </c>
       <c r="E81" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F81" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G81" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H81" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I81" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>91</v>
       </c>
@@ -5618,19 +5653,19 @@
         <v>44104</v>
       </c>
       <c r="E82" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F82" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G82" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I82" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>92</v>
       </c>
@@ -5644,25 +5679,25 @@
         <v>45961</v>
       </c>
       <c r="E83" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F83" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G83" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H83" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="I83" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J83" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>93</v>
       </c>
@@ -5676,25 +5711,25 @@
         <v>47788</v>
       </c>
       <c r="E84" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F84" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G84" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H84" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I84" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J84" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>94</v>
       </c>
@@ -5708,22 +5743,22 @@
         <v>44650</v>
       </c>
       <c r="E85" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F85" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G85" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="I85" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K85" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>95</v>
       </c>
@@ -5737,28 +5772,28 @@
         <v>44865</v>
       </c>
       <c r="E86" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F86" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G86" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H86" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="I86" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="J86" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K86" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>96</v>
       </c>
@@ -5772,28 +5807,28 @@
         <v>45016</v>
       </c>
       <c r="E87" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F87" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G87" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H87" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="I87" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="J87" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K87" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>97</v>
       </c>
@@ -5807,28 +5842,28 @@
         <v>46844</v>
       </c>
       <c r="E88" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F88" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G88" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H88" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="I88" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="J88" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K88" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>98</v>
       </c>
@@ -5842,22 +5877,22 @@
         <v>44681</v>
       </c>
       <c r="E89" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F89" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G89" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I89" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K89" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>99</v>
       </c>
@@ -5871,22 +5906,22 @@
         <v>45016</v>
       </c>
       <c r="E90" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F90" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G90" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="I90" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K90" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>100</v>
       </c>
@@ -5900,22 +5935,22 @@
         <v>46844</v>
       </c>
       <c r="E91" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F91" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G91" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="I91" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K91" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>101</v>
       </c>
@@ -5929,22 +5964,22 @@
         <v>45869</v>
       </c>
       <c r="E92" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F92" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G92" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="I92" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J92" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>102</v>
       </c>
@@ -5958,22 +5993,22 @@
         <v>45199</v>
       </c>
       <c r="E93" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F93" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G93" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I93" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K93" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>103</v>
       </c>
@@ -5987,25 +6022,25 @@
         <v>45869</v>
       </c>
       <c r="E94" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F94" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G94" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="I94" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J94" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K94" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>104</v>
       </c>
@@ -6019,25 +6054,25 @@
         <v>47696</v>
       </c>
       <c r="E95" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F95" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G95" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="I95" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J95" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K95" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>105</v>
       </c>
@@ -6048,19 +6083,19 @@
         <v>43466</v>
       </c>
       <c r="E96" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F96" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G96" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="I96" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>106</v>
       </c>
@@ -6074,19 +6109,19 @@
         <v>44500</v>
       </c>
       <c r="E97" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F97" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G97" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="I97" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>107</v>
       </c>
@@ -6100,19 +6135,19 @@
         <v>45657</v>
       </c>
       <c r="E98" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F98" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G98" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="I98" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>108</v>
       </c>
@@ -6126,25 +6161,25 @@
         <v>44115</v>
       </c>
       <c r="E99" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F99" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G99" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H99" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="I99" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="K99" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>109</v>
       </c>
@@ -6158,28 +6193,28 @@
         <v>45138</v>
       </c>
       <c r="E100" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F100" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G100" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H100" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="I100" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J100" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="K100" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>110</v>
       </c>
@@ -6193,28 +6228,28 @@
         <v>45292</v>
       </c>
       <c r="E101" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F101" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G101" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H101" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="I101" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="J101" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="K101" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>111</v>
       </c>
@@ -6225,19 +6260,19 @@
         <v>43971</v>
       </c>
       <c r="E102" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F102" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G102" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="I102" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>112</v>
       </c>
@@ -6251,22 +6286,22 @@
         <v>46022</v>
       </c>
       <c r="E103" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F103" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G103" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H103" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="I103" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>113</v>
       </c>
@@ -6280,22 +6315,22 @@
         <v>45901</v>
       </c>
       <c r="E104" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F104" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G104" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H104" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="I104" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>114</v>
       </c>
@@ -6309,25 +6344,25 @@
         <v>45657</v>
       </c>
       <c r="E105" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F105" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G105" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="H105" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I105" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K105" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>115</v>
       </c>
@@ -6341,25 +6376,25 @@
         <v>45754</v>
       </c>
       <c r="E106" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F106" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G106" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H106" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I106" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K106" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>116</v>
       </c>
@@ -6373,25 +6408,25 @@
         <v>46022</v>
       </c>
       <c r="E107" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F107" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G107" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H107" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I107" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K107" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>117</v>
       </c>
@@ -6405,25 +6440,25 @@
         <v>47848</v>
       </c>
       <c r="E108" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F108" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G108" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H108" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I108" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K108" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>118</v>
       </c>
@@ -6437,25 +6472,25 @@
         <v>45747</v>
       </c>
       <c r="E109" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F109" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G109" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H109" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="I109" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K109" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>119</v>
       </c>
@@ -6469,25 +6504,25 @@
         <v>47574</v>
       </c>
       <c r="E110" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F110" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G110" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H110" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="I110" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K110" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>120</v>
       </c>
@@ -6501,19 +6536,19 @@
         <v>46935</v>
       </c>
       <c r="E111" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F111" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G111" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="I111" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>121</v>
       </c>
@@ -6527,28 +6562,28 @@
         <v>46934</v>
       </c>
       <c r="E112" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F112" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G112" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="H112" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I112" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J112" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K112" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>122</v>
       </c>
@@ -6562,28 +6597,28 @@
         <v>45930</v>
       </c>
       <c r="E113" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F113" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G113" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="H113" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I113" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J113" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K113" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>123</v>
       </c>
@@ -6597,28 +6632,28 @@
         <v>46022</v>
       </c>
       <c r="E114" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F114" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G114" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="H114" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I114" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J114" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K114" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>124</v>
       </c>
@@ -6632,28 +6667,28 @@
         <v>47848</v>
       </c>
       <c r="E115" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F115" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G115" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H115" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I115" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J115" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K115" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>125</v>
       </c>
@@ -6667,28 +6702,28 @@
         <v>45657</v>
       </c>
       <c r="E116" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F116" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G116" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H116" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I116" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J116" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K116" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>126</v>
       </c>
@@ -6702,28 +6737,28 @@
         <v>45930</v>
       </c>
       <c r="E117" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F117" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G117" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H117" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I117" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J117" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K117" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>127</v>
       </c>
@@ -6737,28 +6772,28 @@
         <v>46022</v>
       </c>
       <c r="E118" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F118" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G118" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="H118" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I118" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J118" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K118" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>128</v>
       </c>
@@ -6772,28 +6807,28 @@
         <v>47848</v>
       </c>
       <c r="E119" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F119" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G119" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="H119" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I119" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J119" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K119" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>129</v>
       </c>
@@ -6807,25 +6842,25 @@
         <v>45838</v>
       </c>
       <c r="E120" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F120" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G120" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I120" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="J120" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K120" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>130</v>
       </c>
@@ -6839,25 +6874,25 @@
         <v>46388</v>
       </c>
       <c r="E121" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G121" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="H121" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="I121" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J121" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K121" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>131</v>
       </c>
@@ -6871,28 +6906,28 @@
         <v>45822</v>
       </c>
       <c r="E122" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F122" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G122" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H122" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I122" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J122" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K122" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>132</v>
       </c>
@@ -6906,28 +6941,28 @@
         <v>46038</v>
       </c>
       <c r="E123" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F123" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G123" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H123" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I123" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J123" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K123" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>133</v>
       </c>
@@ -6941,28 +6976,28 @@
         <v>47848</v>
       </c>
       <c r="E124" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F124" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G124" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H124" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I124" t="s">
+        <v>529</v>
+      </c>
+      <c r="J124" t="s">
         <v>532</v>
       </c>
-      <c r="J124" t="s">
-        <v>535</v>
-      </c>
       <c r="K124" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>134</v>
       </c>
@@ -6976,28 +7011,28 @@
         <v>45822</v>
       </c>
       <c r="E125" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F125" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G125" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H125" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I125" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J125" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K125" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>135</v>
       </c>
@@ -7011,28 +7046,28 @@
         <v>46038</v>
       </c>
       <c r="E126" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F126" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G126" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H126" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I126" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J126" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K126" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>135</v>
       </c>
@@ -7046,28 +7081,28 @@
         <v>47848</v>
       </c>
       <c r="E127" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F127" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G127" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H127" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I127" t="s">
+        <v>529</v>
+      </c>
+      <c r="J127" t="s">
         <v>532</v>
       </c>
-      <c r="J127" t="s">
-        <v>535</v>
-      </c>
       <c r="K127" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>136</v>
       </c>
@@ -7081,22 +7116,22 @@
         <v>47118</v>
       </c>
       <c r="E128" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F128" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G128" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="I128" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K128" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>137</v>
       </c>
@@ -7110,28 +7145,28 @@
         <v>46038</v>
       </c>
       <c r="E129" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F129" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G129" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H129" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I129" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J129" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="K129" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>138</v>
       </c>
@@ -7145,28 +7180,28 @@
         <v>47848</v>
       </c>
       <c r="E130" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F130" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G130" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H130" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I130" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="J130" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="K130" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>139</v>
       </c>
@@ -7180,25 +7215,25 @@
         <v>47848</v>
       </c>
       <c r="E131" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F131" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G131" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="H131" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="I131" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K131" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>140</v>
       </c>
@@ -7212,25 +7247,25 @@
         <v>47848</v>
       </c>
       <c r="E132" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F132" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G132" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="H132" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="I132" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K132" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>141</v>
       </c>
@@ -7244,22 +7279,22 @@
         <v>47848</v>
       </c>
       <c r="E133" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F133" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G133" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="H133" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="I133" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K133" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>

--- a/rules_data/Fiche_BAR.xlsx
+++ b/rules_data/Fiche_BAR.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LoïcGORMAND\Documents\Archives\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BD6C4C9-0602-4346-8433-D571302DCE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1007,6 +1001,18 @@
 ▪ si cas installatation individuelle :
 ▪ la classe énergétique
 ▪ la puissance pondérée en WThC pour un T4 avec sdb et WC</t>
+  </si>
+  <si>
+    <t>▪ Nombre de caissons
+▪ Nombre de bouche d'exctraction
+▪ Nombre d'entrée d'air
+▪ Marque des entrées d'air
+▪ Référence des entrées d'air
+▪ Marque des bouches d'exctraction
+▪ Référence des bouches d'exctraction
+▪ Marque des caissons
+▪ Référence des caissons
+▪ Puissance électrique pondérée absorbée</t>
   </si>
   <si>
     <t>▪ Nombre de PAC air/air installées
@@ -1470,14 +1476,10 @@
 ▪ nombre de logements en installation collective</t>
   </si>
   <si>
-    <t>▪ Type d'énergie de chauffage
-▪ Surface habitable (installation individuelle) ou nombre de logements (installation collective)</t>
+    <t>▪ Surface habitable (installation individuelle) ou nombre de logements (installation collective)</t>
   </si>
   <si>
     <t>▪ Type de ventilation
-▪ Type d'énergie de chauffage
-▪ Numéro de l'avis technique
-▪ Date de validité de l'avis technique
 ▪ Surface habitable (installation individuelle) ou nombre de logements (installation collective)</t>
   </si>
   <si>
@@ -2934,27 +2936,15 @@
     <t>BAR-TH-169
 BAR-TH-178</t>
   </si>
-  <si>
-    <t>▪ Nombre de caissons
-▪ Nombre de bouche d'exctraction
-▪ Nombre d'entrée d'air
-▪ Marque des entrées d'air
-▪ Référence des entrées d'air
-▪ Marque des bouches d'exctraction
-▪ Référence des bouches d'exctraction
-▪ Marque des caissons
-▪ Référence des caissons
-▪ Puissance électrique pondérée absorbée</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2983,33 +2973,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3047,7 +3026,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -3081,7 +3060,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3116,10 +3094,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3292,17 +3269,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K133"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="44.44140625" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" customWidth="1"/>
-    <col min="5" max="5" width="65.5546875" customWidth="1"/>
-    <col min="6" max="6" width="53.33203125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3337,7 +3308,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3354,19 +3325,19 @@
         <v>203</v>
       </c>
       <c r="F2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I2" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -3383,22 +3354,22 @@
         <v>204</v>
       </c>
       <c r="F3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J3" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -3415,22 +3386,22 @@
         <v>205</v>
       </c>
       <c r="F4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="I4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J4" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -3447,22 +3418,22 @@
         <v>205</v>
       </c>
       <c r="F5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J5" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -3479,19 +3450,19 @@
         <v>206</v>
       </c>
       <c r="G6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J6" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3508,19 +3479,19 @@
         <v>206</v>
       </c>
       <c r="G7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J7" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -3537,22 +3508,22 @@
         <v>207</v>
       </c>
       <c r="F8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I8" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J8" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -3569,19 +3540,19 @@
         <v>208</v>
       </c>
       <c r="F9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H9" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J9" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -3598,19 +3569,19 @@
         <v>208</v>
       </c>
       <c r="F10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J10" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3627,16 +3598,16 @@
         <v>207</v>
       </c>
       <c r="F11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I11" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -3653,22 +3624,22 @@
         <v>209</v>
       </c>
       <c r="F12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H12" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I12" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J12" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -3685,22 +3656,22 @@
         <v>210</v>
       </c>
       <c r="F13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H13" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J13" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -3717,22 +3688,22 @@
         <v>210</v>
       </c>
       <c r="F14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H14" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I14" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J14" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -3749,22 +3720,22 @@
         <v>210</v>
       </c>
       <c r="F15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H15" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I15" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J15" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -3781,19 +3752,19 @@
         <v>211</v>
       </c>
       <c r="F16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I16" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J16" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3810,22 +3781,22 @@
         <v>212</v>
       </c>
       <c r="F17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H17" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I17" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J17" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -3842,16 +3813,16 @@
         <v>207</v>
       </c>
       <c r="F18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I18" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -3868,19 +3839,19 @@
         <v>207</v>
       </c>
       <c r="F19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H19" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I19" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -3897,22 +3868,22 @@
         <v>207</v>
       </c>
       <c r="F20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G20" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H20" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I20" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J20" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -3929,22 +3900,22 @@
         <v>207</v>
       </c>
       <c r="F21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H21" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I21" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J21" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -3961,19 +3932,19 @@
         <v>213</v>
       </c>
       <c r="F22" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G22" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I22" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K22" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -3990,22 +3961,22 @@
         <v>213</v>
       </c>
       <c r="F23" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G23" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K23" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -4022,22 +3993,22 @@
         <v>214</v>
       </c>
       <c r="F24" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G24" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H24" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I24" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K24" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -4054,16 +4025,16 @@
         <v>215</v>
       </c>
       <c r="F25" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G25" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I25" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -4080,16 +4051,16 @@
         <v>216</v>
       </c>
       <c r="F26" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G26" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I26" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -4103,16 +4074,16 @@
         <v>217</v>
       </c>
       <c r="F27" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G27" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I27" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -4126,16 +4097,16 @@
         <v>218</v>
       </c>
       <c r="F28" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G28" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I28" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -4152,19 +4123,19 @@
         <v>219</v>
       </c>
       <c r="F29" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G29" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I29" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -4181,19 +4152,19 @@
         <v>219</v>
       </c>
       <c r="F30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G30" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H30" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I30" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -4210,19 +4181,19 @@
         <v>220</v>
       </c>
       <c r="F31" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G31" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H31" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I31" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
         <v>41</v>
       </c>
@@ -4239,19 +4210,19 @@
         <v>221</v>
       </c>
       <c r="F32" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G32" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H32" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I32" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -4268,19 +4239,19 @@
         <v>221</v>
       </c>
       <c r="F33" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G33" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H33" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I33" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
         <v>43</v>
       </c>
@@ -4297,19 +4268,19 @@
         <v>221</v>
       </c>
       <c r="F34" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G34" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H34" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I34" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -4326,19 +4297,19 @@
         <v>222</v>
       </c>
       <c r="F35" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G35" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I35" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K35" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -4355,16 +4326,16 @@
         <v>223</v>
       </c>
       <c r="G36" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H36" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I36" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -4381,19 +4352,19 @@
         <v>223</v>
       </c>
       <c r="G37" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H37" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I37" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K37" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" t="s">
         <v>47</v>
       </c>
@@ -4407,19 +4378,19 @@
         <v>224</v>
       </c>
       <c r="F38" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G38" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I38" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K38" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -4436,16 +4407,16 @@
         <v>225</v>
       </c>
       <c r="F39" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G39" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I39" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
         <v>49</v>
       </c>
@@ -4462,22 +4433,22 @@
         <v>226</v>
       </c>
       <c r="F40" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G40" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H40" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I40" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J40" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -4494,19 +4465,19 @@
         <v>227</v>
       </c>
       <c r="F41" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G41" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I41" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J41" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -4523,19 +4494,19 @@
         <v>228</v>
       </c>
       <c r="F42" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G42" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I42" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J42" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
         <v>52</v>
       </c>
@@ -4552,19 +4523,19 @@
         <v>229</v>
       </c>
       <c r="F43" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G43" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I43" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J43" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -4578,16 +4549,16 @@
         <v>230</v>
       </c>
       <c r="F44" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G44" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I44" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
         <v>54</v>
       </c>
@@ -4604,16 +4575,16 @@
         <v>231</v>
       </c>
       <c r="F45" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G45" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I45" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -4630,19 +4601,19 @@
         <v>232</v>
       </c>
       <c r="F46" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G46" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H46" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I46" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
         <v>56</v>
       </c>
@@ -4659,22 +4630,22 @@
         <v>233</v>
       </c>
       <c r="F47" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G47" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H47" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I47" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J47" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -4691,13 +4662,13 @@
         <v>234</v>
       </c>
       <c r="G48" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I48" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
         <v>58</v>
       </c>
@@ -4714,19 +4685,19 @@
         <v>235</v>
       </c>
       <c r="F49" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G49" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H49" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I49" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -4743,22 +4714,22 @@
         <v>236</v>
       </c>
       <c r="F50" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G50" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H50" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I50" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J50" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -4775,25 +4746,25 @@
         <v>237</v>
       </c>
       <c r="F51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G51" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H51" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I51" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J51" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K51" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -4807,19 +4778,19 @@
         <v>238</v>
       </c>
       <c r="F52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G52" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I52" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K52" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" t="s">
         <v>62</v>
       </c>
@@ -4836,19 +4807,19 @@
         <v>239</v>
       </c>
       <c r="F53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G53" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I53" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K53" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" t="s">
         <v>63</v>
       </c>
@@ -4865,16 +4836,16 @@
         <v>240</v>
       </c>
       <c r="F54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G54" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I54" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" t="s">
         <v>64</v>
       </c>
@@ -4891,19 +4862,19 @@
         <v>241</v>
       </c>
       <c r="F55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G55" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I55" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K55" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11">
       <c r="A56" t="s">
         <v>65</v>
       </c>
@@ -4920,19 +4891,19 @@
         <v>242</v>
       </c>
       <c r="F56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G56" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="I56" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K56" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -4949,16 +4920,16 @@
         <v>243</v>
       </c>
       <c r="F57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G57" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I57" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
         <v>67</v>
       </c>
@@ -4975,22 +4946,22 @@
         <v>244</v>
       </c>
       <c r="F58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G58" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H58" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I58" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J58" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" t="s">
         <v>68</v>
       </c>
@@ -5007,22 +4978,22 @@
         <v>245</v>
       </c>
       <c r="F59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G59" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H59" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I59" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J59" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="144" x14ac:dyDescent="0.3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -5035,20 +5006,20 @@
       <c r="D60" s="1">
         <v>43921</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>568</v>
+      <c r="E60" t="s">
+        <v>246</v>
       </c>
       <c r="F60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G60" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I60" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="144" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
         <v>70</v>
       </c>
@@ -5061,26 +5032,26 @@
       <c r="D61" s="1">
         <v>45291</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>568</v>
+      <c r="E61" t="s">
+        <v>246</v>
       </c>
       <c r="F61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G61" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H61" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I61" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J61" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="144" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -5093,26 +5064,26 @@
       <c r="D62" s="1">
         <v>46934</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>568</v>
+      <c r="E62" t="s">
+        <v>246</v>
       </c>
       <c r="F62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G62" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H62" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I62" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J62" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
         <v>72</v>
       </c>
@@ -5123,19 +5094,19 @@
         <v>43191</v>
       </c>
       <c r="E63" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G63" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I63" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64" t="s">
         <v>73</v>
       </c>
@@ -5149,19 +5120,19 @@
         <v>45291</v>
       </c>
       <c r="E64" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G64" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I64" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -5175,19 +5146,19 @@
         <v>46753</v>
       </c>
       <c r="E65" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G65" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I65" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" t="s">
         <v>75</v>
       </c>
@@ -5201,19 +5172,19 @@
         <v>44104</v>
       </c>
       <c r="E66" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G66" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I66" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67" t="s">
         <v>76</v>
       </c>
@@ -5227,19 +5198,19 @@
         <v>44804</v>
       </c>
       <c r="E67" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F67" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G67" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I67" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -5253,19 +5224,19 @@
         <v>46022</v>
       </c>
       <c r="E68" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F68" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G68" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I68" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -5276,19 +5247,19 @@
         <v>46023</v>
       </c>
       <c r="E69" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F69" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G69" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I69" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -5299,19 +5270,19 @@
         <v>42767</v>
       </c>
       <c r="E70" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F70" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G70" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I70" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -5325,22 +5296,22 @@
         <v>45992</v>
       </c>
       <c r="E71" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F71" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G71" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I71" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K71" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -5354,28 +5325,28 @@
         <v>47848</v>
       </c>
       <c r="E72" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G72" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H72" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I72" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J72" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K72" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -5389,22 +5360,22 @@
         <v>43921</v>
       </c>
       <c r="E73" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F73" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G73" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I73" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K73" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -5418,28 +5389,28 @@
         <v>45138</v>
       </c>
       <c r="E74" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G74" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H74" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I74" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J74" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K74" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -5453,28 +5424,28 @@
         <v>45596</v>
       </c>
       <c r="E75" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F75" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G75" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H75" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I75" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J75" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K75" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -5488,19 +5459,19 @@
         <v>45960</v>
       </c>
       <c r="E76" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F76" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G76" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I76" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -5514,22 +5485,22 @@
         <v>46022</v>
       </c>
       <c r="E77" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F77" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G77" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H77" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I77" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -5543,25 +5514,25 @@
         <v>47848</v>
       </c>
       <c r="E78" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F78" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G78" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H78" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I78" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K78" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -5575,19 +5546,19 @@
         <v>45901</v>
       </c>
       <c r="E79" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F79" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G79" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I79" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -5601,19 +5572,19 @@
         <v>43921</v>
       </c>
       <c r="E80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F80" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G80" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I80" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
       <c r="A81" t="s">
         <v>90</v>
       </c>
@@ -5624,22 +5595,22 @@
         <v>43922</v>
       </c>
       <c r="E81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F81" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G81" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H81" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I81" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82" t="s">
         <v>91</v>
       </c>
@@ -5653,19 +5624,19 @@
         <v>44104</v>
       </c>
       <c r="E82" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F82" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G82" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I82" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
       <c r="A83" t="s">
         <v>92</v>
       </c>
@@ -5679,25 +5650,25 @@
         <v>45961</v>
       </c>
       <c r="E83" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F83" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G83" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H83" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I83" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J83" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
       <c r="A84" t="s">
         <v>93</v>
       </c>
@@ -5711,25 +5682,25 @@
         <v>47788</v>
       </c>
       <c r="E84" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F84" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G84" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H84" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I84" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J84" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
       <c r="A85" t="s">
         <v>94</v>
       </c>
@@ -5743,22 +5714,22 @@
         <v>44650</v>
       </c>
       <c r="E85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F85" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G85" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I85" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K85" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
       <c r="A86" t="s">
         <v>95</v>
       </c>
@@ -5772,28 +5743,28 @@
         <v>44865</v>
       </c>
       <c r="E86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F86" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G86" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H86" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I86" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J86" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K86" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
       <c r="A87" t="s">
         <v>96</v>
       </c>
@@ -5807,28 +5778,28 @@
         <v>45016</v>
       </c>
       <c r="E87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F87" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G87" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H87" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I87" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J87" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K87" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
       <c r="A88" t="s">
         <v>97</v>
       </c>
@@ -5842,28 +5813,28 @@
         <v>46844</v>
       </c>
       <c r="E88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F88" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G88" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H88" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I88" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J88" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K88" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
       <c r="A89" t="s">
         <v>98</v>
       </c>
@@ -5877,22 +5848,22 @@
         <v>44681</v>
       </c>
       <c r="E89" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F89" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G89" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I89" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K89" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
       <c r="A90" t="s">
         <v>99</v>
       </c>
@@ -5906,22 +5877,22 @@
         <v>45016</v>
       </c>
       <c r="E90" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F90" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G90" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I90" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K90" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
       <c r="A91" t="s">
         <v>100</v>
       </c>
@@ -5935,22 +5906,22 @@
         <v>46844</v>
       </c>
       <c r="E91" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F91" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G91" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I91" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K91" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
       <c r="A92" t="s">
         <v>101</v>
       </c>
@@ -5964,22 +5935,22 @@
         <v>45869</v>
       </c>
       <c r="E92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F92" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G92" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I92" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J92" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
       <c r="A93" t="s">
         <v>102</v>
       </c>
@@ -5993,22 +5964,22 @@
         <v>45199</v>
       </c>
       <c r="E93" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F93" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G93" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I93" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K93" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
       <c r="A94" t="s">
         <v>103</v>
       </c>
@@ -6022,25 +5993,25 @@
         <v>45869</v>
       </c>
       <c r="E94" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F94" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G94" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I94" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J94" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K94" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
       <c r="A95" t="s">
         <v>104</v>
       </c>
@@ -6054,25 +6025,25 @@
         <v>47696</v>
       </c>
       <c r="E95" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F95" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G95" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I95" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J95" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K95" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
       <c r="A96" t="s">
         <v>105</v>
       </c>
@@ -6083,19 +6054,19 @@
         <v>43466</v>
       </c>
       <c r="E96" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F96" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G96" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I96" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
       <c r="A97" t="s">
         <v>106</v>
       </c>
@@ -6109,19 +6080,19 @@
         <v>44500</v>
       </c>
       <c r="E97" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F97" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G97" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I97" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
       <c r="A98" t="s">
         <v>107</v>
       </c>
@@ -6135,19 +6106,19 @@
         <v>45657</v>
       </c>
       <c r="E98" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F98" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G98" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I98" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
       <c r="A99" t="s">
         <v>108</v>
       </c>
@@ -6161,25 +6132,25 @@
         <v>44115</v>
       </c>
       <c r="E99" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F99" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G99" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H99" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I99" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K99" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
       <c r="A100" t="s">
         <v>109</v>
       </c>
@@ -6193,28 +6164,28 @@
         <v>45138</v>
       </c>
       <c r="E100" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F100" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G100" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H100" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I100" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="J100" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K100" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
       <c r="A101" t="s">
         <v>110</v>
       </c>
@@ -6228,28 +6199,28 @@
         <v>45292</v>
       </c>
       <c r="E101" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F101" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G101" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H101" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I101" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J101" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K101" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
       <c r="A102" t="s">
         <v>111</v>
       </c>
@@ -6260,19 +6231,19 @@
         <v>43971</v>
       </c>
       <c r="E102" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F102" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G102" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I102" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
       <c r="A103" t="s">
         <v>112</v>
       </c>
@@ -6286,22 +6257,22 @@
         <v>46022</v>
       </c>
       <c r="E103" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F103" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G103" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H103" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I103" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
       <c r="A104" t="s">
         <v>113</v>
       </c>
@@ -6315,22 +6286,22 @@
         <v>45901</v>
       </c>
       <c r="E104" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F104" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G104" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H104" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I104" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
       <c r="A105" t="s">
         <v>114</v>
       </c>
@@ -6344,25 +6315,25 @@
         <v>45657</v>
       </c>
       <c r="E105" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F105" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G105" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H105" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I105" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K105" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
       <c r="A106" t="s">
         <v>115</v>
       </c>
@@ -6376,25 +6347,25 @@
         <v>45754</v>
       </c>
       <c r="E106" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F106" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G106" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H106" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I106" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K106" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
       <c r="A107" t="s">
         <v>116</v>
       </c>
@@ -6408,25 +6379,25 @@
         <v>46022</v>
       </c>
       <c r="E107" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F107" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G107" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H107" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I107" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K107" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
       <c r="A108" t="s">
         <v>117</v>
       </c>
@@ -6440,25 +6411,25 @@
         <v>47848</v>
       </c>
       <c r="E108" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F108" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G108" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H108" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I108" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K108" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
       <c r="A109" t="s">
         <v>118</v>
       </c>
@@ -6472,25 +6443,25 @@
         <v>45747</v>
       </c>
       <c r="E109" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F109" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G109" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H109" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I109" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K109" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
       <c r="A110" t="s">
         <v>119</v>
       </c>
@@ -6504,25 +6475,25 @@
         <v>47574</v>
       </c>
       <c r="E110" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F110" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G110" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H110" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I110" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K110" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
       <c r="A111" t="s">
         <v>120</v>
       </c>
@@ -6536,19 +6507,19 @@
         <v>46935</v>
       </c>
       <c r="E111" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F111" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G111" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I111" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
       <c r="A112" t="s">
         <v>121</v>
       </c>
@@ -6562,28 +6533,28 @@
         <v>46934</v>
       </c>
       <c r="E112" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F112" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G112" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H112" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I112" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J112" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K112" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
       <c r="A113" t="s">
         <v>122</v>
       </c>
@@ -6597,28 +6568,28 @@
         <v>45930</v>
       </c>
       <c r="E113" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F113" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G113" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H113" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I113" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J113" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K113" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
       <c r="A114" t="s">
         <v>123</v>
       </c>
@@ -6632,28 +6603,28 @@
         <v>46022</v>
       </c>
       <c r="E114" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F114" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G114" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H114" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I114" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J114" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K114" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
       <c r="A115" t="s">
         <v>124</v>
       </c>
@@ -6667,28 +6638,28 @@
         <v>47848</v>
       </c>
       <c r="E115" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F115" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G115" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H115" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I115" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J115" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K115" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
       <c r="A116" t="s">
         <v>125</v>
       </c>
@@ -6702,28 +6673,28 @@
         <v>45657</v>
       </c>
       <c r="E116" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F116" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G116" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H116" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I116" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J116" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K116" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
       <c r="A117" t="s">
         <v>126</v>
       </c>
@@ -6737,28 +6708,28 @@
         <v>45930</v>
       </c>
       <c r="E117" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F117" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G117" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H117" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I117" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J117" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K117" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
       <c r="A118" t="s">
         <v>127</v>
       </c>
@@ -6772,28 +6743,28 @@
         <v>46022</v>
       </c>
       <c r="E118" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F118" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G118" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H118" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I118" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J118" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K118" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
       <c r="A119" t="s">
         <v>128</v>
       </c>
@@ -6807,28 +6778,28 @@
         <v>47848</v>
       </c>
       <c r="E119" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F119" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G119" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H119" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I119" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J119" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K119" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
       <c r="A120" t="s">
         <v>129</v>
       </c>
@@ -6842,25 +6813,25 @@
         <v>45838</v>
       </c>
       <c r="E120" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F120" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G120" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I120" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J120" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K120" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
       <c r="A121" t="s">
         <v>130</v>
       </c>
@@ -6874,25 +6845,25 @@
         <v>46388</v>
       </c>
       <c r="E121" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G121" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H121" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I121" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J121" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K121" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
       <c r="A122" t="s">
         <v>131</v>
       </c>
@@ -6906,28 +6877,28 @@
         <v>45822</v>
       </c>
       <c r="E122" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F122" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G122" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H122" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I122" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J122" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K122" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
       <c r="A123" t="s">
         <v>132</v>
       </c>
@@ -6941,28 +6912,28 @@
         <v>46038</v>
       </c>
       <c r="E123" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F123" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G123" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H123" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I123" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J123" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K123" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
       <c r="A124" t="s">
         <v>133</v>
       </c>
@@ -6976,28 +6947,28 @@
         <v>47848</v>
       </c>
       <c r="E124" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F124" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G124" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H124" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I124" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J124" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K124" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
       <c r="A125" t="s">
         <v>134</v>
       </c>
@@ -7011,28 +6982,28 @@
         <v>45822</v>
       </c>
       <c r="E125" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F125" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G125" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H125" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I125" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J125" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K125" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
       <c r="A126" t="s">
         <v>135</v>
       </c>
@@ -7046,28 +7017,28 @@
         <v>46038</v>
       </c>
       <c r="E126" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F126" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G126" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H126" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I126" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J126" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K126" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
       <c r="A127" t="s">
         <v>135</v>
       </c>
@@ -7081,28 +7052,28 @@
         <v>47848</v>
       </c>
       <c r="E127" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F127" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G127" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H127" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I127" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J127" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K127" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
       <c r="A128" t="s">
         <v>136</v>
       </c>
@@ -7116,22 +7087,22 @@
         <v>47118</v>
       </c>
       <c r="E128" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F128" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G128" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I128" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K128" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
       <c r="A129" t="s">
         <v>137</v>
       </c>
@@ -7145,28 +7116,28 @@
         <v>46038</v>
       </c>
       <c r="E129" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F129" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G129" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H129" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I129" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J129" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K129" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
       <c r="A130" t="s">
         <v>138</v>
       </c>
@@ -7180,28 +7151,28 @@
         <v>47848</v>
       </c>
       <c r="E130" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F130" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G130" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H130" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I130" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J130" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K130" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
       <c r="A131" t="s">
         <v>139</v>
       </c>
@@ -7215,25 +7186,25 @@
         <v>47848</v>
       </c>
       <c r="E131" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F131" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G131" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H131" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I131" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K131" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
       <c r="A132" t="s">
         <v>140</v>
       </c>
@@ -7247,25 +7218,25 @@
         <v>47848</v>
       </c>
       <c r="E132" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F132" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G132" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H132" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I132" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K132" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
       <c r="A133" t="s">
         <v>141</v>
       </c>
@@ -7279,22 +7250,22 @@
         <v>47848</v>
       </c>
       <c r="E133" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F133" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G133" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H133" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I133" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K133" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
